--- a/data/visits/Visits_2026-09-15.xlsx
+++ b/data/visits/Visits_2026-09-15.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,11 +435,11 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -559,20 +559,16 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3577</t>
-        </is>
+      <c r="C2" t="n">
+        <v>3577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Muhammad Faizan</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
+      <c r="E2" t="n">
+        <v>123456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -585,13 +581,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>24.83751303141844</v>
+        <v>24.83751303</v>
       </c>
       <c r="I2" t="n">
-        <v>67.0339194845166</v>
+        <v>67.03391947999999</v>
       </c>
       <c r="J2" t="n">
-        <v>49.98464589770236</v>
+        <v>49.9846459</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -607,8 +603,67 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIS-20260915222126-840655</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>117865</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ammar petroleum</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:21:26</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>24.9775717</v>
+      </c>
+      <c r="I3" t="n">
+        <v>67.186125</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.199999809265137</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S2"/>
+  <autoFilter ref="A1:S3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>